--- a/products-storage/06-id-blokiruet-oplatu/07-grafik-ustraneniya.xlsx
+++ b/products-storage/06-id-blokiruet-oplatu/07-grafik-ustraneniya.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2">
-        <f>СРЗНАЧ(G2:G20)</f>
+        <f>AVERAGE(G2:G3)</f>
         <v/>
       </c>
       <c r="H4" s="2" t="inlineStr"/>

--- a/products-storage/06-id-blokiruet-oplatu/07-grafik-ustraneniya.xlsx
+++ b/products-storage/06-id-blokiruet-oplatu/07-grafik-ustraneniya.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2">
-        <f>AVERAGE(G2:G3)</f>
+        <f>СРЗНАЧ(G2:G20)</f>
         <v/>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
